--- a/datasets/day1_excel_foundations/01_interface_and_workbook_basics/d1_m1_interface_answers.xlsx
+++ b/datasets/day1_excel_foundations/01_interface_and_workbook_basics/d1_m1_interface_answers.xlsx
@@ -538,7 +538,7 @@
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>119.7</v>
+        <v>120</v>
       </c>
     </row>
     <row r="4">
@@ -569,7 +569,7 @@
         <v>2</v>
       </c>
       <c r="G4" t="n">
-        <v>3332</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="5">
@@ -600,7 +600,7 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>1454.4</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="6">
@@ -631,7 +631,7 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>806</v>
+        <v>600</v>
       </c>
     </row>
     <row r="7">
@@ -662,7 +662,7 @@
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1656</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="8">
@@ -693,7 +693,7 @@
         <v>3</v>
       </c>
       <c r="G8" t="n">
-        <v>326.25</v>
+        <v>300</v>
       </c>
     </row>
     <row r="9">
@@ -724,7 +724,7 @@
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>779.2</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="10">
@@ -755,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="G10" t="n">
-        <v>587.2</v>
+        <v>600</v>
       </c>
     </row>
     <row r="11">
@@ -786,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="G11" t="n">
-        <v>801.6</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="12">
@@ -817,7 +817,7 @@
         <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>1663</v>
+        <v>1400</v>
       </c>
     </row>
     <row r="13">
@@ -848,7 +848,7 @@
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>1037</v>
+        <v>600</v>
       </c>
     </row>
   </sheetData>

--- a/datasets/day1_excel_foundations/01_interface_and_workbook_basics/d1_m1_interface_answers.xlsx
+++ b/datasets/day1_excel_foundations/01_interface_and_workbook_basics/d1_m1_interface_answers.xlsx
@@ -435,7 +435,7 @@
   <cols>
     <col width="10.5" customWidth="1" min="1" max="1"/>
     <col width="13.5" customWidth="1" min="2" max="2"/>
-    <col width="16.5" customWidth="1" min="3" max="3"/>
+    <col width="19.5" customWidth="1" min="3" max="3"/>
     <col width="22.5" customWidth="1" min="4" max="4"/>
     <col width="12.5" customWidth="1" min="5" max="5"/>
     <col width="10.5" customWidth="1" min="6" max="6"/>
@@ -566,10 +566,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>3000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="5">
@@ -597,10 +597,10 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G5" t="n">
-        <v>1400</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="6">
@@ -619,19 +619,19 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>OnePlus 13</t>
+          <t>iPad Air 6</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>600</v>
+        <v>700</v>
       </c>
     </row>
     <row r="7">
@@ -641,28 +641,28 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45938</v>
+        <v>45694</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amara Otieno</t>
+          <t>Simbarashe Mutasa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Galaxy S24</t>
+          <t>Ring Doorbell Pro</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="F7" t="n">
         <v>2</v>
       </c>
       <c r="G7" t="n">
-        <v>1600</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8">
@@ -672,28 +672,28 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45458</v>
+        <v>45922</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chanda Phiri</t>
+          <t>Rutendo Chikafu</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Echo Dot 6</t>
+          <t>Galaxy S24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Smart Home</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>300</v>
+        <v>800</v>
       </c>
     </row>
     <row r="9">
@@ -734,28 +734,28 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45856</v>
+        <v>46084</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Chipo Marufu</t>
+          <t>Nyasha Banda</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>USB-C Hub 7in1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Accessory</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G10" t="n">
-        <v>600</v>
+        <v>160</v>
       </c>
     </row>
     <row r="11">
@@ -765,28 +765,28 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45383</v>
+        <v>45796</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Nyasha Banda</t>
+          <t>Farai Ncube</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>HP Spectre x360</t>
+          <t>Surface Go 4</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>1200</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="12">
@@ -796,28 +796,28 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>46317</v>
+        <v>46200</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kudzai Sibanda</t>
+          <t>Thabo Nkosi</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ThinkPad X1</t>
+          <t>Pixel 9 Pro</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G12" t="n">
-        <v>1400</v>
+        <v>1800</v>
       </c>
     </row>
     <row r="13">
@@ -827,28 +827,28 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45857</v>
+        <v>45944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tendai Moyo</t>
+          <t>Kagiso Molefe</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Surface Go 4</t>
+          <t>Echo Dot 6</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Smart Home</t>
         </is>
       </c>
       <c r="F13" t="n">
         <v>1</v>
       </c>
       <c r="G13" t="n">
-        <v>600</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
